--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N105_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.09516773291975</v>
+        <v>5.052964756599459</v>
       </c>
       <c r="D2" t="n">
-        <v>30.97141003367006</v>
+        <v>5.032854130471386</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
